--- a/output/Resumen_comercial.xlsx
+++ b/output/Resumen_comercial.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1014598</v>
+        <v>1320447</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>212982638</v>
+        <v>111697370</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finanzas</t>
+          <t>Ventas</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Híbrido</t>
+          <t>Presencial</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
